--- a/charlie-ingest/tests/fixtures/resolution.xlsx
+++ b/charlie-ingest/tests/fixtures/resolution.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="TaxRate">Data!$H$1</definedName>
-    <definedName name="AllQ1">Data!$B$2:$B$4</definedName>
+    <definedName name="AllQOne">Data!$B$2:$B$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,7 +500,7 @@
         <v/>
       </c>
       <c r="H3">
-        <f>SUM(AllQ1)</f>
+        <f>SUM(AllQOne)</f>
         <v/>
       </c>
     </row>
